--- a/request_forms/017_data_porting_intake_form--request_forms.xlsx
+++ b/request_forms/017_data_porting_intake_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>requestor_email</t>
+          <t>requestor_email_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Requestor Email</t>
+          <t>Requestor Email 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Transfer Date</t>
+          <t>Transfer Date (2)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>transfer_time</t>
+          <t>transfer_time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Transfer Time</t>
+          <t>Transfer Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>notes_2</t>
+          <t>notes_2_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>requestor_work_phone</t>
+          <t>requestor_work_phone_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Requestor Work Phone</t>
+          <t>Requestor Work Phone 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'email_and_phone'}</t>
+          <t>email_and_phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Email and Phone'}</t>
+          <t>Email and Phone</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'email,_phone,_and_in-person'}</t>
+          <t>email,_phone,_and_in-person</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Email, Phone, and In-Person'}</t>
+          <t>Email, Phone, and In-Person</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'phone_and_in-person'}</t>
+          <t>phone_and_in-person</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Phone and In-Person'}</t>
+          <t>Phone and In-Person</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'In-Person'}</t>
+          <t>In-Person</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'data_transfers'}</t>
+          <t>data_transfers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Data Transfers'}</t>
+          <t>Data Transfers</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'account_information'}</t>
+          <t>account_information</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Account Information'}</t>
+          <t>Account Information</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'account_management'}</t>
+          <t>account_management</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Account Management'}</t>
+          <t>Account Management</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Multiple'}</t>
+          <t>Multiple</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
